--- a/output/quickfixclose7_portfolio_daily.xlsx
+++ b/output/quickfixclose7_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>172,903.57</t>
+          <t>201,701.33</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+72.90%</t>
+          <t>+101.70%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>178,776  (+78.78%)</t>
+          <t>208,805  (+108.81%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,698  (5.9 pts of return)</t>
+          <t>3,973  (7.1 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.9x</t>
+          <t>5.4x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+6.12R  (best +17.09R)</t>
+          <t>+6.36R  (best +17.09R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6,165  (+6.12%)</t>
+          <t>6,896  (+6.36%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,273  (-1.29%)</t>
+          <t>-1,285  (-1.29%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>77% of trading days</t>
+          <t>78% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5695,22 +5695,70 @@
         <v>46234</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>172903.57</v>
+        <v>173064.32</v>
       </c>
       <c r="C186" s="5" t="n">
+        <v>6652.41</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>166411.92</v>
+      </c>
+      <c r="E186" t="n">
+        <v>4</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>173064.32</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>6652.41</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>166411.92</v>
+      </c>
+      <c r="E187" t="n">
+        <v>4</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>201701.33</v>
+      </c>
+      <c r="C188" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D186" s="5" t="n">
-        <v>172903.57</v>
-      </c>
-      <c r="E186" t="n">
+      <c r="D188" s="5" t="n">
+        <v>201701.33</v>
+      </c>
+      <c r="E188" t="n">
         <v>0</v>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT exit_close (+21,286); Corn_CBOT_Futures exit_close (+9,321); NY_Natural_Gas_Futures stop (-1,950); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -9754,14 +9802,22 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>7</v>
+      </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>12.755</v>
       </c>
       <c r="G79" t="n">
-        <v>0.019</v>
+        <v>0.038</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.019</v>
+        <v>12.717</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>191671.72</v>
@@ -9769,15 +9825,15 @@
       <c r="J79" s="5" t="n">
         <v>2664.24</v>
       </c>
-      <c r="K79" s="6" t="n">
-        <v>-50.27</v>
+      <c r="K79" s="7" t="n">
+        <v>33881.01</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>200541.97</v>
+        <v>234473.24</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -9797,14 +9853,22 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>7</v>
+      </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>5.675</v>
       </c>
       <c r="G80" t="n">
-        <v>0.025</v>
+        <v>0.05</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.025</v>
+        <v>5.625</v>
       </c>
       <c r="I80" s="5" t="n">
         <v>189007.49</v>
@@ -9812,15 +9876,15 @@
       <c r="J80" s="5" t="n">
         <v>2627.2</v>
       </c>
-      <c r="K80" s="6" t="n">
-        <v>-65.68000000000001</v>
+      <c r="K80" s="7" t="n">
+        <v>14778.02</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>200476.29</v>
+        <v>249251.27</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9923,7 @@
         <v>-32.38</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>200336.76</v>
+        <v>246111.63</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -9883,14 +9947,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4</v>
+      </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.04</v>
+        <v>-1.16</v>
       </c>
       <c r="I82" s="5" t="n">
         <v>192710.11</v>
@@ -9899,14 +9971,14 @@
         <v>2678.67</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>-107.15</v>
+        <v>-3107.26</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>200369.14</v>
+        <v>246144.01</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>stop</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose7_portfolio_daily.xlsx
+++ b/output/quickfixclose7_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>201,701.33</t>
+          <t>234,542.19</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+101.70%</t>
+          <t>+134.54%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>208,805  (+108.81%)</t>
+          <t>242,760  (+142.76%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,973  (7.1 pts of return)</t>
+          <t>4,004  (8.2 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5.4x</t>
+          <t>7.2x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3.8 bars</t>
+          <t>3.9 bars</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+6.36R  (best +17.09R)</t>
+          <t>+6.89R  (best +20.01R)</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6,896  (+6.36%)</t>
+          <t>7,894  (+6.89%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5743,22 +5743,82 @@
         <v>46238</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>201701.33</v>
+        <v>201721.83</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>0</v>
+        <v>1640.53</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>201701.33</v>
+        <v>200081.3</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT exit_close (+21,286); Corn_CBOT_Futures exit_close (+9,321); NY_Natural_Gas_Futures stop (-1,950); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT exit_close (+21,286); Corn_CBOT_Futures exit_close (+9,321); NY_Natural_Gas_Futures stop (-1,950)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>201721.83</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>7583.15</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>194138.69</v>
+      </c>
+      <c r="E189" t="n">
+        <v>4</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 2,001); Nasdaq_100_E_mini short (risk 1,981); S_P_500_E_mini short (risk 1,961)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>234542.19</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>234542.19</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 1,941)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures exit_close (+32,831)</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9904,14 +9964,22 @@
           <t>2026-07-28</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>7</v>
+      </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>20.038</v>
       </c>
       <c r="G81" t="n">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.013</v>
+        <v>20.013</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>186380.28</v>
@@ -9919,15 +9987,15 @@
       <c r="J81" s="5" t="n">
         <v>2590.69</v>
       </c>
-      <c r="K81" s="6" t="n">
-        <v>-32.38</v>
+      <c r="K81" s="7" t="n">
+        <v>51846.1</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>246111.63</v>
+        <v>297971.93</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -9979,6 +10047,178 @@
       <c r="M82" t="inlineStr">
         <is>
           <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>243553.32</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>3385.39</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>-11.75</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>246126.52</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>240167.93</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>3338.33</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>246138.28</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>236829.6</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>3291.93</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>246125.82</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>233537.67</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>3246.17</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>-5.55</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>246138.46</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose7_portfolio_daily.xlsx
+++ b/output/quickfixclose7_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>234,542.19</t>
+          <t>232,575.92</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+134.54%</t>
+          <t>+132.58%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>242,760  (+142.76%)</t>
+          <t>240,750  (+140.75%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4,004  (8.2 pts of return)</t>
+          <t>4,029  (8.2 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7.2x</t>
+          <t>7.1x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>31.7%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3.9 bars</t>
+          <t>3.8 bars</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,285  (-1.29%)</t>
+          <t>-1,297  (-1.28%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5799,26 +5799,58 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>234542.19</v>
+        <v>234552.98</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>7884</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>226668.98</v>
+      </c>
+      <c r="E190" t="n">
+        <v>4</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 1,941)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures exit_close (+32,831)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>232575.92</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>234542.19</v>
-      </c>
-      <c r="E190" t="n">
+      <c r="D191" s="5" t="n">
+        <v>232575.92</v>
+      </c>
+      <c r="E191" t="n">
         <v>0</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 1,941)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures exit_close (+32,831)</t>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 2,267); NY_Palladium_Futures short (risk 2,244)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX stop (-1,955); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9991,7 +10023,7 @@
         <v>51846.1</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>297971.93</v>
+        <v>297990.11</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -10085,7 +10117,7 @@
         <v>-11.75</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>246126.52</v>
+        <v>294683.8</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -10128,7 +10160,7 @@
         <v>-0.18</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>246138.28</v>
+        <v>294721.56</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -10171,7 +10203,7 @@
         <v>-0.7</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>246125.82</v>
+        <v>294683.11</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -10195,14 +10227,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G86" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I86" s="5" t="n">
         <v>233537.67</v>
@@ -10211,12 +10251,98 @@
         <v>3246.17</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>-5.55</v>
+        <v>-3268.37</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>246138.46</v>
+        <v>294721.74</v>
       </c>
       <c r="M86" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>284728.28</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>3957.72</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>294710.86</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>280770.56</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>3902.71</v>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>294695.56</v>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
